--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/phi-4/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/phi-4/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.4748201438848921</v>
+        <v>0.4130434782608696</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.4788732394366197</v>
+        <v>0.4225352112676056</v>
       </c>
       <c r="D2">
-        <v>0.5285714285714286</v>
+        <v>0.5899280575539568</v>
       </c>
       <c r="E2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
